--- a/static/format-upload/template-import-sellings-rkef.xlsx
+++ b/static/format-upload/template-import-sellings-rkef.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meinardus.bria\Desktop\SQMS - Python imports\format-downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\meinardus.bria\django_project\alpha\static\format-upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE06533B-18EC-41A9-9B45-E856294593AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69595603-79B8-4925-BA3F-D1B5E2863859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="530" xr2:uid="{164D2D34-7551-47B0-9F6A-8815E64D8F5F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="530" xr2:uid="{164D2D34-7551-47B0-9F6A-8815E64D8F5F}"/>
   </bookViews>
   <sheets>
     <sheet name="import_rkef" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">import_rkef!$A$1:$Y$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">import_rkef!$A$1:$X$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>material</t>
   </si>
@@ -50,9 +50,6 @@
     <t>shift</t>
   </si>
   <si>
-    <t>stockpile_ori</t>
-  </si>
-  <si>
     <t>dome_ori</t>
   </si>
   <si>
@@ -141,9 +138,6 @@
   </si>
   <si>
     <t>01/009</t>
-  </si>
-  <si>
-    <t>SS_05</t>
   </si>
   <si>
     <t>T14_M</t>
@@ -275,7 +269,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -326,27 +320,6 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -664,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87B3D86-194F-4428-914C-7EAEEB34E444}">
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.140625" style="6" bestFit="1" customWidth="1"/>
@@ -674,44 +647,43 @@
     <col min="5" max="5" width="11.140625" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8" style="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.85546875" style="6" customWidth="1"/>
-    <col min="23" max="23" width="15" style="6" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="15.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="6"/>
+    <col min="8" max="8" width="10.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8" style="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.85546875" style="6" customWidth="1"/>
+    <col min="22" max="22" width="15" style="6" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="15.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" s="5" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>0</v>
@@ -725,17 +697,17 @@
       <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O1" s="4" t="s">
         <v>21</v>
@@ -744,10 +716,10 @@
         <v>22</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>13</v>
@@ -767,49 +739,46 @@
       <c r="X1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="2" spans="1:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>45658</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>36</v>
       </c>
       <c r="N2" s="8" t="s">
         <v>31</v>
@@ -818,37 +787,34 @@
         <v>32</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" s="13">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="13">
         <v>45531</v>
       </c>
+      <c r="R2" s="9">
+        <v>46130</v>
+      </c>
       <c r="S2" s="9">
-        <v>46130</v>
+        <v>69420</v>
       </c>
       <c r="T2" s="9">
-        <v>69420</v>
-      </c>
-      <c r="U2" s="9">
         <v>23290</v>
       </c>
+      <c r="U2" s="15" t="s">
+        <v>37</v>
+      </c>
       <c r="V2" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="W2" s="15" t="s">
-        <v>40</v>
+        <v>38</v>
+      </c>
+      <c r="W2" s="16">
+        <v>45531.873923611114</v>
       </c>
       <c r="X2" s="16">
-        <v>45531.873923611114</v>
-      </c>
-      <c r="Y2" s="16">
         <v>45658.899722222224</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -861,21 +827,20 @@
       <c r="J3" s="12"/>
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
+      <c r="M3" s="11"/>
       <c r="N3" s="11"/>
       <c r="O3" s="11"/>
       <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="12"/>
       <c r="S3" s="12"/>
       <c r="T3" s="12"/>
-      <c r="U3" s="12"/>
+      <c r="U3" s="17"/>
       <c r="V3" s="17"/>
-      <c r="W3" s="17"/>
+      <c r="W3" s="18"/>
       <c r="X3" s="18"/>
-      <c r="Y3" s="18"/>
     </row>
-    <row r="4" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -888,48 +853,46 @@
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
       <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
+      <c r="M4" s="8"/>
       <c r="N4" s="8"/>
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="9"/>
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
+      <c r="U4" s="15"/>
       <c r="V4" s="15"/>
-      <c r="W4" s="15"/>
+      <c r="W4" s="16"/>
       <c r="X4" s="16"/>
-      <c r="Y4" s="16"/>
     </row>
-    <row r="5" spans="1:25" s="25" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="19"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="21"/>
-      <c r="M5" s="21"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="21"/>
-      <c r="T5" s="21"/>
-      <c r="U5" s="21"/>
-      <c r="V5" s="23"/>
-      <c r="W5" s="23"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="24"/>
+    <row r="5" spans="1:24" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="14"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="18"/>
+      <c r="X5" s="18"/>
     </row>
-    <row r="6" spans="1:25" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -942,22 +905,21 @@
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
       <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
+      <c r="M6" s="8"/>
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="9"/>
       <c r="S6" s="9"/>
       <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
+      <c r="U6" s="15"/>
       <c r="V6" s="15"/>
-      <c r="W6" s="15"/>
+      <c r="W6" s="16"/>
       <c r="X6" s="16"/>
-      <c r="Y6" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Y6" xr:uid="{B87B3D86-194F-4428-914C-7EAEEB34E444}"/>
+  <autoFilter ref="A1:X6" xr:uid="{B87B3D86-194F-4428-914C-7EAEEB34E444}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
